--- a/static.xlsx
+++ b/static.xlsx
@@ -4,6 +4,9 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="F1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="F2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="O1" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="O5M" sheetId="4" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,21 +14,258 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>test1</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>test4</t>
-  </si>
-  <si>
-    <t>test5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+  <si>
+    <t>fff1</t>
+  </si>
+  <si>
+    <t>fff2</t>
+  </si>
+  <si>
+    <t>fff3</t>
+  </si>
+  <si>
+    <t>fff4</t>
+  </si>
+  <si>
+    <t>fff5</t>
+  </si>
+  <si>
+    <t>fff6</t>
+  </si>
+  <si>
+    <t>fff7</t>
+  </si>
+  <si>
+    <t>fff8</t>
+  </si>
+  <si>
+    <t>fff9</t>
+  </si>
+  <si>
+    <t>fff10</t>
+  </si>
+  <si>
+    <t>fff11</t>
+  </si>
+  <si>
+    <t>fff12</t>
+  </si>
+  <si>
+    <t>fff13</t>
+  </si>
+  <si>
+    <t>fff14</t>
+  </si>
+  <si>
+    <t>fff15</t>
+  </si>
+  <si>
+    <t>fff16</t>
+  </si>
+  <si>
+    <t>fff17</t>
+  </si>
+  <si>
+    <t>fff18</t>
+  </si>
+  <si>
+    <t>fff19</t>
+  </si>
+  <si>
+    <t>fff20</t>
+  </si>
+  <si>
+    <t>fff21</t>
+  </si>
+  <si>
+    <t>fffff_1</t>
+  </si>
+  <si>
+    <t>ffff_2</t>
+  </si>
+  <si>
+    <t>fffff_2</t>
+  </si>
+  <si>
+    <t>ffff_3</t>
+  </si>
+  <si>
+    <t>fffff_3</t>
+  </si>
+  <si>
+    <t>ffff_4</t>
+  </si>
+  <si>
+    <t>fffff_4</t>
+  </si>
+  <si>
+    <t>ffff_5</t>
+  </si>
+  <si>
+    <t>fffff_5</t>
+  </si>
+  <si>
+    <t>ffff_6</t>
+  </si>
+  <si>
+    <t>fffff_6</t>
+  </si>
+  <si>
+    <t>ffff_7</t>
+  </si>
+  <si>
+    <t>fffff_7</t>
+  </si>
+  <si>
+    <t>ffff_8</t>
+  </si>
+  <si>
+    <t>fffff_8</t>
+  </si>
+  <si>
+    <t>ffff_9</t>
+  </si>
+  <si>
+    <t>fffff_9</t>
+  </si>
+  <si>
+    <t>ffff_10</t>
+  </si>
+  <si>
+    <t>fffff_10</t>
+  </si>
+  <si>
+    <t>ffff_11</t>
+  </si>
+  <si>
+    <t>fffff_11</t>
+  </si>
+  <si>
+    <t>oo1</t>
+  </si>
+  <si>
+    <t>oo2</t>
+  </si>
+  <si>
+    <t>oo3</t>
+  </si>
+  <si>
+    <t>oo4</t>
+  </si>
+  <si>
+    <t>oo5</t>
+  </si>
+  <si>
+    <t>oo6</t>
+  </si>
+  <si>
+    <t>oo7</t>
+  </si>
+  <si>
+    <t>oo8</t>
+  </si>
+  <si>
+    <t>oo9</t>
+  </si>
+  <si>
+    <t>oo10</t>
+  </si>
+  <si>
+    <t>oo11</t>
+  </si>
+  <si>
+    <t>oo12</t>
+  </si>
+  <si>
+    <t>oo13</t>
+  </si>
+  <si>
+    <t>oo14</t>
+  </si>
+  <si>
+    <t>oo15</t>
+  </si>
+  <si>
+    <t>oo16</t>
+  </si>
+  <si>
+    <t>oo17</t>
+  </si>
+  <si>
+    <t>oo18</t>
+  </si>
+  <si>
+    <t>oo19</t>
+  </si>
+  <si>
+    <t>oo20</t>
+  </si>
+  <si>
+    <t>oo21</t>
+  </si>
+  <si>
+    <t>o55_1</t>
+  </si>
+  <si>
+    <t>o55_2</t>
+  </si>
+  <si>
+    <t>o55_3</t>
+  </si>
+  <si>
+    <t>o55_4</t>
+  </si>
+  <si>
+    <t>o55_5</t>
+  </si>
+  <si>
+    <t>o55_6</t>
+  </si>
+  <si>
+    <t>o55_7</t>
+  </si>
+  <si>
+    <t>o55_8</t>
+  </si>
+  <si>
+    <t>o55_9</t>
+  </si>
+  <si>
+    <t>o55_10</t>
+  </si>
+  <si>
+    <t>o55_11</t>
+  </si>
+  <si>
+    <t>o55_12</t>
+  </si>
+  <si>
+    <t>o55_13</t>
+  </si>
+  <si>
+    <t>o55_14</t>
+  </si>
+  <si>
+    <t>o55_15</t>
+  </si>
+  <si>
+    <t>o55_16</t>
+  </si>
+  <si>
+    <t>o55_17</t>
+  </si>
+  <si>
+    <t>o55_18</t>
+  </si>
+  <si>
+    <t>o55_19</t>
+  </si>
+  <si>
+    <t>o55_20</t>
+  </si>
+  <si>
+    <t>o55_21</t>
   </si>
 </sst>
 </file>
@@ -75,6 +315,18 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -323,6 +575,674 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/static.xlsx
+++ b/static.xlsx
@@ -7,13 +7,19 @@
     <sheet state="visible" name="O1" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="F2" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="O2" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="F4" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="O4M" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="O4W" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="F5M" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="F5W" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="O5M" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="O5W" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="F3" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="O3" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="F4" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="O4M" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="O4W" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="F5M" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="F5W" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="O5M" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="O5W" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="F6M" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="F6W" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="O6M" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="O6W" sheetId="17" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -21,28 +27,394 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="5">
-  <si>
-    <t>TEST1</t>
-  </si>
-  <si>
-    <t>TEST2</t>
-  </si>
-  <si>
-    <t>TEST3</t>
-  </si>
-  <si>
-    <t>TEST4</t>
-  </si>
-  <si>
-    <t>TEST5</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>アラタ タクミ</t>
+  </si>
+  <si>
+    <t>サイトウ リュウシン</t>
+  </si>
+  <si>
+    <t>ビトウ エイト</t>
+  </si>
+  <si>
+    <t>モリタ リリ</t>
+  </si>
+  <si>
+    <t>イノウエ エイト</t>
+  </si>
+  <si>
+    <t>シモナガ ルルア</t>
+  </si>
+  <si>
+    <t>ハマイ チカホ</t>
+  </si>
+  <si>
+    <t>ミズシマ リョウセイ</t>
+  </si>
+  <si>
+    <t>アトキ エイタロウ</t>
+  </si>
+  <si>
+    <t>オオハシ　カナト</t>
+  </si>
+  <si>
+    <t>ゴトウ　カエデ</t>
+  </si>
+  <si>
+    <t>マツモト コハル</t>
+  </si>
+  <si>
+    <t>マルハシ シュンペイ</t>
+  </si>
+  <si>
+    <t>ヤマグチ ホダカ</t>
+  </si>
+  <si>
+    <t>ヤマグチ　ヨウタ</t>
+  </si>
+  <si>
+    <t>ヤマモト　ショウセイ</t>
+  </si>
+  <si>
+    <t>ヤマモト　ハルヒ</t>
+  </si>
+  <si>
+    <t>ヨコヤマ　ニナ</t>
+  </si>
+  <si>
+    <t>ツマガリ カズホ</t>
+  </si>
+  <si>
+    <t>テラダ タクロウ</t>
+  </si>
+  <si>
+    <t>イイダ ヒカリ</t>
+  </si>
+  <si>
+    <t>キムラ サツキ</t>
+  </si>
+  <si>
+    <t>キムラ マサキ</t>
+  </si>
+  <si>
+    <t>コバヤシ ユズハ</t>
+  </si>
+  <si>
+    <t>サイトウ テッシン</t>
+  </si>
+  <si>
+    <t>タケダ コウタロウ</t>
+  </si>
+  <si>
+    <t>ナカヤマ コウスケ</t>
+  </si>
+  <si>
+    <t>ハタケヤマ タカシ</t>
+  </si>
+  <si>
+    <t>ハヤタ アンナ</t>
+  </si>
+  <si>
+    <t>ホラグチ ノノコ</t>
+  </si>
+  <si>
+    <t>ホワン ジャリャン(黃 家梁)</t>
+  </si>
+  <si>
+    <t>マツモト ユウキ</t>
+  </si>
+  <si>
+    <t>ミシナ リオ</t>
+  </si>
+  <si>
+    <t>ミツイシ ユイ</t>
+  </si>
+  <si>
+    <t>モモキ ミノリ</t>
+  </si>
+  <si>
+    <t>ヤマシロ マリン</t>
+  </si>
+  <si>
+    <t>ヨシオカ トウマ</t>
+  </si>
+  <si>
+    <t>ナカニシ カンナ</t>
+  </si>
+  <si>
+    <t>ハマイ ツムギ</t>
+  </si>
+  <si>
+    <t>ヤマダ セイカ</t>
+  </si>
+  <si>
+    <t>ヤマナカ キョウスケ</t>
+  </si>
+  <si>
+    <t>アオキ ショウタロウ</t>
+  </si>
+  <si>
+    <t>アリモト タケル</t>
+  </si>
+  <si>
+    <t>イズミ コウタロウ</t>
+  </si>
+  <si>
+    <t>イノウエ ユウト</t>
+  </si>
+  <si>
+    <t>ウラカミ イチカ</t>
+  </si>
+  <si>
+    <t>カユカワ リク</t>
+  </si>
+  <si>
+    <t>コイケ  エイイチロウ</t>
+  </si>
+  <si>
+    <t>サカタ ガク</t>
+  </si>
+  <si>
+    <t>シモダ ソラト</t>
+  </si>
+  <si>
+    <t>ハラシマ アサヒ</t>
+  </si>
+  <si>
+    <t>ホワン ジャドン(黃 家棟)</t>
+  </si>
+  <si>
+    <t>ヨネバヤシ タクト</t>
+  </si>
+  <si>
+    <t>イケダ マナ</t>
+  </si>
+  <si>
+    <t>ウノカワ ミワ</t>
+  </si>
+  <si>
+    <t>オオイケ ユヅキ</t>
+  </si>
+  <si>
+    <t>オオミナト ツバサ</t>
+  </si>
+  <si>
+    <t>カワナミ リンコ</t>
+  </si>
+  <si>
+    <t>クスミ ミツキ</t>
+  </si>
+  <si>
+    <t>シンジョウ ハヅキ</t>
+  </si>
+  <si>
+    <t>スギムラ コト</t>
+  </si>
+  <si>
+    <t>セキネ ノア</t>
+  </si>
+  <si>
+    <t>タニグチ リン</t>
+  </si>
+  <si>
+    <t>ハタヤマ ヒヨリ</t>
+  </si>
+  <si>
+    <t>バン ヒヨリ</t>
+  </si>
+  <si>
+    <t>ヤマグチ ミツキ</t>
+  </si>
+  <si>
+    <t>カイノ アサヒ</t>
+  </si>
+  <si>
+    <t>ムラタ ハル</t>
+  </si>
+  <si>
+    <t>ウチダ ケイタ</t>
+  </si>
+  <si>
+    <t>オオイ ヒビキ</t>
+  </si>
+  <si>
+    <t>オカモト リント</t>
+  </si>
+  <si>
+    <t>キムラ コウイチロウ</t>
+  </si>
+  <si>
+    <t>コスゲ サク</t>
+  </si>
+  <si>
+    <t>ソノダ エイト</t>
+  </si>
+  <si>
+    <t>ナカヤマ ケイスケ</t>
+  </si>
+  <si>
+    <t>ノガミ エイスケ</t>
+  </si>
+  <si>
+    <t>ハラダ セイタ</t>
+  </si>
+  <si>
+    <t>ビトウ リクト</t>
+  </si>
+  <si>
+    <t>フルカワ ミナト</t>
+  </si>
+  <si>
+    <t>マルヤマ ジュンペイ</t>
+  </si>
+  <si>
+    <t>ミヤモト ツバサ</t>
+  </si>
+  <si>
+    <t>ムラグチ エイタロウ</t>
+  </si>
+  <si>
+    <t>ヤマグチ ハヤト</t>
+  </si>
+  <si>
+    <t>ヨシオカ ハルキ</t>
+  </si>
+  <si>
+    <t>アラタ　キコ</t>
+  </si>
+  <si>
+    <t>オオノ　ノゾミ</t>
+  </si>
+  <si>
+    <t>カサハラ スイ</t>
+  </si>
+  <si>
+    <t>カトウ　ヒカリ</t>
+  </si>
+  <si>
+    <t>カワチ カリン</t>
+  </si>
+  <si>
+    <t>サイトウ カコ</t>
+  </si>
+  <si>
+    <t>シバヤマ　ミウ</t>
+  </si>
+  <si>
+    <t>トクナガ　ナノハ</t>
+  </si>
+  <si>
+    <t>ナカジマスミレ</t>
+  </si>
+  <si>
+    <t>ニシグチ　リナ</t>
+  </si>
+  <si>
+    <t>ハマダ サアヤ</t>
+  </si>
+  <si>
+    <t>ミマ ノンノ</t>
+  </si>
+  <si>
+    <t>モリ　カンナ</t>
+  </si>
+  <si>
+    <t>ヨコヤマ　ハナ</t>
+  </si>
+  <si>
+    <t>アオキ リンタロウ</t>
+  </si>
+  <si>
+    <t>イケダ コテツ</t>
+  </si>
+  <si>
+    <t>コウヤマ キョウノスケ</t>
+  </si>
+  <si>
+    <t>サクラバ イッセイ</t>
+  </si>
+  <si>
+    <t>タカギ ガク</t>
+  </si>
+  <si>
+    <t>テシマ ユウト</t>
+  </si>
+  <si>
+    <t>ナガイ ケンシロウ</t>
+  </si>
+  <si>
+    <t>ハットリ コウタ</t>
+  </si>
+  <si>
+    <t>ハママツ ショウタロウ</t>
+  </si>
+  <si>
+    <t>ハヤシ タイチ</t>
+  </si>
+  <si>
+    <t>マツヤマ ホタカ</t>
+  </si>
+  <si>
+    <t>エゴ リイサ</t>
+  </si>
+  <si>
+    <t>カネイリサワ</t>
+  </si>
+  <si>
+    <t>カモイ ミサキ</t>
+  </si>
+  <si>
+    <t>クヤ キノ</t>
+  </si>
+  <si>
+    <t>ゴトウ マナカ</t>
+  </si>
+  <si>
+    <t>コンドウ リンカ</t>
+  </si>
+  <si>
+    <t>サトウ リミ</t>
+  </si>
+  <si>
+    <t>シモナガ リリア</t>
+  </si>
+  <si>
+    <t>ナカハラ リンカ</t>
+  </si>
+  <si>
+    <t>ニシカワ ヒロノ</t>
+  </si>
+  <si>
+    <t>ニワ ハルノ</t>
+  </si>
+  <si>
+    <t>フクイ カリン</t>
+  </si>
+  <si>
+    <t>ホリイ ユウ</t>
+  </si>
+  <si>
+    <t>マエカワ アサヒ</t>
+  </si>
+  <si>
+    <t>モモキ ハナミ</t>
+  </si>
+  <si>
+    <t>ヤマガミ サラ</t>
+  </si>
+  <si>
+    <t>ワダ スミレ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -54,6 +426,23 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF434343"/>
+      <name val="ＭＳ ゴシック"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -63,18 +452,104 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border/>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -93,6 +568,30 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -341,38 +840,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -389,40 +856,8 @@
       <c r="A1" s="1">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B1" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -441,40 +876,8 @@
       <c r="A1" s="1">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B1" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -482,7 +885,280 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -497,44 +1173,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -549,44 +1193,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -597,40 +1209,88 @@
       <c r="A1" s="1">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+      <c r="B4" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>5.0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -638,7 +1298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -649,40 +1309,344 @@
       <c r="A1" s="1">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+      <c r="B4" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1">
         <v>5.0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -698,43 +1662,139 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1">
+      <c r="A1" s="3">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="3">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>5.0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -750,43 +1810,35 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1">
+      <c r="A1" s="6">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="6">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="6">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="6">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -802,43 +1854,99 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1">
+      <c r="A1" s="6">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="6">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="6">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="6">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="6">
         <v>5.0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -854,43 +1962,107 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1">
+      <c r="A1" s="6">
         <v>1.0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+      <c r="B1" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="6">
         <v>2.0</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3" s="6">
         <v>3.0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4" s="6">
         <v>4.0</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
+      <c r="B4" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5" s="6">
         <v>5.0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <v>13.0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/static.xlsx
+++ b/static.xlsx
@@ -1,28 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the6/the6/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4685CB01-4CF7-423F-A55A-CD68953C2DA8}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="F1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="O1" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="F2" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="O2" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="F3" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="O3" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="F4" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="O4M" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="O4W" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="F5M" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="F5W" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="O5M" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="O5W" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="F6M" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="F6W" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="O6M" sheetId="16" r:id="rId20"/>
-    <sheet state="visible" name="O6W" sheetId="17" r:id="rId21"/>
+    <sheet name="F1" sheetId="1" r:id="rId1"/>
+    <sheet name="O1" sheetId="2" r:id="rId2"/>
+    <sheet name="F2" sheetId="3" r:id="rId3"/>
+    <sheet name="O2" sheetId="4" r:id="rId4"/>
+    <sheet name="F3" sheetId="5" r:id="rId5"/>
+    <sheet name="O3" sheetId="6" r:id="rId6"/>
+    <sheet name="F4" sheetId="7" r:id="rId7"/>
+    <sheet name="O4M" sheetId="8" r:id="rId8"/>
+    <sheet name="O4W" sheetId="9" r:id="rId9"/>
+    <sheet name="F5M" sheetId="10" r:id="rId10"/>
+    <sheet name="F5W" sheetId="11" r:id="rId11"/>
+    <sheet name="O5M" sheetId="12" r:id="rId12"/>
+    <sheet name="O5W" sheetId="13" r:id="rId13"/>
+    <sheet name="F6M" sheetId="14" r:id="rId14"/>
+    <sheet name="F6W" sheetId="15" r:id="rId15"/>
+    <sheet name="O6M" sheetId="16" r:id="rId16"/>
+    <sheet name="O6W" sheetId="17" r:id="rId17"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -56,9 +65,6 @@
     <t>ミズシマ リョウセイ</t>
   </si>
   <si>
-    <t>アトキ エイタロウ</t>
-  </si>
-  <si>
     <t>オオハシ　カナト</t>
   </si>
   <si>
@@ -408,40 +414,61 @@
   </si>
   <si>
     <t>ワダ スミレ</t>
+  </si>
+  <si>
+    <t>アオキ エイタロウ</t>
+    <phoneticPr fontId="6"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -449,11 +476,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
@@ -467,6 +500,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -481,6 +515,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -495,6 +530,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -509,130 +545,58 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -822,1250 +786,1286 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>67</v>
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>68</v>
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6"/>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="9" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="9" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B13" s="9" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>14</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6"/>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="11" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="3">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>17.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6">
-        <v>1.0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2">
+        <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="6"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/static.xlsx
+++ b/static.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the6/the6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4685CB01-4CF7-423F-A55A-CD68953C2DA8}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{493AD41D-6FF1-46B3-BF46-022B6DAEA35D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
   <si>
     <t>-</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>ハマイ チカホ</t>
-  </si>
-  <si>
-    <t>ミズシマ リョウセイ</t>
   </si>
   <si>
     <t>オオハシ　カナト</t>
@@ -593,6 +590,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -826,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -878,7 +879,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -886,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -894,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -902,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -910,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -918,7 +919,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -926,7 +927,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -934,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -942,7 +943,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -950,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -958,7 +959,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -966,7 +967,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -974,7 +975,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -982,7 +983,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -990,7 +991,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1015,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1023,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1031,7 +1032,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1039,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1047,7 +1048,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1055,7 +1056,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1063,7 +1064,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1071,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1079,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1087,7 +1088,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1095,7 +1096,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1103,7 +1104,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1111,7 +1112,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1119,7 +1120,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1191,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1199,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1207,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1215,7 +1216,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1223,7 +1224,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1231,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1239,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1247,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1255,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1263,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1271,7 +1272,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1293,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1301,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1309,7 +1310,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1317,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1325,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1333,7 +1334,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1341,7 +1342,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1349,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1357,7 +1358,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1365,7 +1366,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1373,7 +1374,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1381,7 +1382,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1389,7 +1390,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1397,7 +1398,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1405,7 +1406,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1413,7 +1414,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -1421,7 +1422,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1509,12 +1510,8 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
@@ -1535,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1543,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1551,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1559,7 +1556,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1567,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1575,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1583,7 +1580,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1591,7 +1588,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1599,7 +1596,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1607,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1637,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1667,7 +1664,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1675,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1683,7 +1680,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1691,7 +1688,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1699,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1707,7 +1704,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1715,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1723,7 +1720,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1731,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1739,7 +1736,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1747,7 +1744,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1755,7 +1752,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1763,7 +1760,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1771,7 +1768,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1779,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -1787,7 +1784,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1817,7 +1814,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1825,7 +1822,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1833,7 +1830,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1863,7 +1860,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1871,7 +1868,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1879,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1887,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1895,7 +1892,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1903,7 +1900,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1911,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1919,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1927,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1935,7 +1932,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1943,7 +1940,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1965,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1973,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1981,7 +1978,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1989,7 +1986,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1997,7 +1994,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2005,7 +2002,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -2013,7 +2010,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -2021,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -2029,7 +2026,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -2037,7 +2034,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -2045,7 +2042,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -2053,7 +2050,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -2061,7 +2058,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/static.xlsx
+++ b/static.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the6/the6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{493AD41D-6FF1-46B3-BF46-022B6DAEA35D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F5E0961-FB3A-460D-9C1B-B6FBE78B7CF2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
   <si>
     <t>-</t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>ハタヤマ ヒヨリ</t>
-  </si>
-  <si>
-    <t>バン ヒヨリ</t>
   </si>
   <si>
     <t>ヤマグチ ミツキ</t>
@@ -416,12 +413,20 @@
     <t>アオキ エイタロウ</t>
     <phoneticPr fontId="6"/>
   </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ユアサ リョウスケ</t>
+    <phoneticPr fontId="6"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -466,6 +471,20 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -548,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -575,6 +594,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -827,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -871,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -879,7 +900,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -887,7 +908,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -895,7 +916,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -903,7 +924,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -911,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -919,7 +940,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -927,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -935,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -943,7 +964,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -951,7 +972,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -959,7 +980,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -967,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -975,7 +996,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -983,7 +1004,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -991,7 +1012,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1016,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1024,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1032,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1040,7 +1061,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1048,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1056,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1064,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1072,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1080,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1088,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1096,7 +1117,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1104,7 +1125,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1112,7 +1133,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1120,7 +1141,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1184,7 +1205,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1192,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1200,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1208,7 +1229,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1216,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1224,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1232,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1240,7 +1261,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1248,7 +1269,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1256,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1264,7 +1285,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1272,7 +1293,15 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>12</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1302,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1310,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1318,7 +1347,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1326,7 +1355,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1334,7 +1363,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1342,7 +1371,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1350,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1358,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1366,7 +1395,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1374,7 +1403,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1382,7 +1411,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1390,7 +1419,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1398,7 +1427,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1406,7 +1435,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1414,7 +1443,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -1422,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2050,7 +2079,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -2058,7 +2087,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/static.xlsx
+++ b/static.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the6/the6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F5E0961-FB3A-460D-9C1B-B6FBE78B7CF2}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F84CB8C5-C6AC-4CA2-8E94-90D373D5FD72}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
   <si>
     <t>-</t>
   </si>
@@ -227,9 +227,6 @@
     <t>ハタヤマ ヒヨリ</t>
   </si>
   <si>
-    <t>ヤマグチ ミツキ</t>
-  </si>
-  <si>
     <t>カイノ アサヒ</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
   </si>
   <si>
     <t>クヤ キノ</t>
-  </si>
-  <si>
-    <t>ゴトウ マナカ</t>
   </si>
   <si>
     <t>コンドウ リンカ</t>
@@ -419,6 +413,10 @@
   </si>
   <si>
     <t>ユアサ リョウスケ</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ヤマグチ ミツキ </t>
     <phoneticPr fontId="6"/>
   </si>
 </sst>
@@ -848,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -900,7 +898,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -908,7 +906,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -916,7 +914,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -924,7 +922,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -932,7 +930,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -940,7 +938,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -948,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -956,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -964,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -972,7 +970,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -980,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -988,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -996,7 +994,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1004,7 +1002,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1012,7 +1010,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1037,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1045,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1053,7 +1051,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1061,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1069,7 +1067,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1077,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1085,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1093,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1101,7 +1099,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1109,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1117,7 +1115,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1125,7 +1123,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1133,7 +1131,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1141,7 +1139,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1208,92 +1206,92 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1301,7 +1299,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1331,7 +1329,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1339,7 +1337,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1347,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1355,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1363,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1371,7 +1369,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1379,7 +1377,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1387,7 +1385,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1395,7 +1393,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1403,7 +1401,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1411,7 +1409,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1419,7 +1417,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -1427,7 +1425,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1435,7 +1433,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -1443,7 +1441,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -1451,7 +1449,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2083,12 +2081,8 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <v>13</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>63</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>

--- a/static.xlsx
+++ b/static.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5c2aa0dda8f38b74/デスクトップ/BPUMP/the6/the6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F84CB8C5-C6AC-4CA2-8E94-90D373D5FD72}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_06D9294D455705A31EA6F67B64A9FCE6BD752BBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3DE9879-1F5A-4510-AE7D-ECAC758B23A3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" firstSheet="5" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
   <si>
     <t>-</t>
   </si>
@@ -405,10 +405,6 @@
   </si>
   <si>
     <t>アオキ エイタロウ</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -1299,7 +1295,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1350,107 +1346,103 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
         <v>17</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>121</v>
       </c>
+    </row>
+    <row r="17" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6"/>
@@ -2077,7 +2069,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
